--- a/docs/hoja.xlsx
+++ b/docs/hoja.xlsx
@@ -648,9 +648,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2597760</xdr:colOff>
+      <xdr:colOff>2597400</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -664,7 +664,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="459720" y="258480"/>
-          <a:ext cx="2339280" cy="622440"/>
+          <a:ext cx="2338920" cy="622080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/docs/hoja.xlsx
+++ b/docs/hoja.xlsx
@@ -9,12 +9,14 @@
   </bookViews>
   <sheets>
     <sheet name="hoja" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="hoja_2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">hoja!$A$2:$I$45</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">hoja_2!$A$2:$I$45</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t xml:space="preserve">FORM-</t>
   </si>
@@ -88,12 +90,18 @@
     <t xml:space="preserve">EMPRESA ESTATAL DE PRODUCCIÓN Y COMERCIALIZACIÓN DEL ORO - EPCORO</t>
   </si>
   <si>
+    <t xml:space="preserve">Caja de Salud</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nº NIM</t>
   </si>
   <si>
     <t xml:space="preserve">02-2388-05</t>
   </si>
   <si>
+    <t xml:space="preserve">Valor Neto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nº NIT</t>
   </si>
   <si>
@@ -103,58 +111,82 @@
     <t xml:space="preserve">CAJA DE SALUD APORTE 1,8%</t>
   </si>
   <si>
+    <t xml:space="preserve">si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOMBRE VENDEDOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARNET DE IDENTIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3. PROCEDENCIA DEL MINERAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOMBRE AREA MINERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TITULAR DE DERECHO MINERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CODIGO UNICO DE LA AJAM PAGO DE PATENTE MINERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPARTAMENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROVINCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUNICIPIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CODIGO DEL MUNICIPIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCALIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. INFORMACIÓN TÉCNICA DEL MINERAL ORO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESENTACIÓN DEL MINERAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORO FUNDIDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESO   (Gramo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEY PAGABLE DEL ORO (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESO FINO (Gr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EP-BCB-723</t>
+  </si>
+  <si>
     <t xml:space="preserve">NO</t>
   </si>
   <si>
-    <t xml:space="preserve">NOMBRE VENDEDOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARNET DE IDENTIDAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3. PROCEDENCIA DEL MINERAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOMBRE AREA MINERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TITULAR DE DERECHO MINERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CODIGO UNICO DE LA AJAM PAGO DE PATENTE MINERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPARTAMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVINCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MUNICIPIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CODIGO DEL MUNICIPIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOCALIDAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. INFORMACIÓN TÉCNICA DEL MINERAL ORO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRESENTACIÓN DEL MINERAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORO FUNDIDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PESO   (Gramo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEY PAGABLE DEL ORO (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PESO FINO (Gr)</t>
+    <t xml:space="preserve">DYONNE LIZET TITO CORTEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COOP. DE EXPLOTACION AURIFERA CHIMA LTDA SECTOR 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COOPERATIVA MINERA CHIMA R.L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA PAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARECAJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIPUANI</t>
   </si>
 </sst>
 </file>
@@ -170,7 +202,7 @@
     <numFmt numFmtId="169" formatCode="0\ %"/>
     <numFmt numFmtId="170" formatCode="0.00\ %"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -265,6 +297,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -363,7 +401,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -556,13 +594,17 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -648,9 +690,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2597400</xdr:colOff>
+      <xdr:colOff>2596320</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -664,7 +706,50 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="459720" y="258480"/>
-          <a:ext cx="2338920" cy="622080"/>
+          <a:ext cx="2337840" cy="621000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>258480</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>68040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2596320</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>188640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="459720" y="258480"/>
+          <a:ext cx="2337840" cy="621000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -977,7 +1062,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1103,24 +1188,37 @@
         <v>19</v>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="21"/>
+      <c r="E11" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <f aca="false">F10*H11</f>
+        <v>19296.3390489972</v>
+      </c>
       <c r="G11" s="13"/>
-      <c r="H11" s="22"/>
+      <c r="H11" s="22" t="n">
+        <f aca="false">IF(C20="NO",0,0.018)</f>
+        <v>0.018</v>
+      </c>
       <c r="I11" s="23"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="14"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <f aca="false">F10-F11</f>
+        <v>1052722.4970064</v>
+      </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -1129,7 +1227,7 @@
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>1006965023</v>
@@ -1205,7 +1303,7 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" s="32"/>
       <c r="D19" s="14"/>
@@ -1219,10 +1317,10 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="9"/>
@@ -1235,7 +1333,7 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" s="29" t="str">
         <f aca="false">[1]NOMBRES!F3</f>
@@ -1252,7 +1350,7 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="38" t="n">
         <f aca="false">[1]NOMBRES!G3</f>
@@ -1305,7 +1403,7 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="14"/>
@@ -1319,7 +1417,7 @@
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" s="41" t="str">
         <f aca="false">[1]NOMBRES!H3</f>
@@ -1336,7 +1434,7 @@
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C28" s="42" t="str">
         <f aca="false">[1]NOMBRES!I3</f>
@@ -1353,7 +1451,7 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="43" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C29" s="39" t="n">
         <f aca="false">[1]NOMBRES!J3</f>
@@ -1370,7 +1468,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="39" t="str">
         <f aca="false">[1]NOMBRES!K3</f>
@@ -1387,7 +1485,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C31" s="39" t="str">
         <f aca="false">[1]NOMBRES!L3</f>
@@ -1404,7 +1502,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C32" s="39" t="str">
         <f aca="false">[1]NOMBRES!M3</f>
@@ -1421,7 +1519,7 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C33" s="39" t="n">
         <f aca="false">[1]NOMBRES!N3</f>
@@ -1438,7 +1536,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C34" s="39" t="str">
         <f aca="false">[1]NOMBRES!O3</f>
@@ -1467,7 +1565,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="14"/>
@@ -1481,10 +1579,10 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C37" s="45" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="9"/>
@@ -1497,7 +1595,7 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C38" s="46" t="n">
         <f aca="false">[1]NOMBRES!P3</f>
@@ -1514,7 +1612,7 @@
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C39" s="47" t="n">
         <f aca="false">[1]NOMBRES!Q3</f>
@@ -1531,7 +1629,7 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C40" s="48" t="n">
         <f aca="false">C39*C38</f>
@@ -1610,4 +1708,681 @@
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF8FAADC"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:J45"/>
+  <sheetFormatPr defaultColWidth="11.00390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="2.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="2.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="str">
+        <f aca="false">C8</f>
+        <v>EP-BCB-723</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="22.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5"/>
+      <c r="C3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7"/>
+      <c r="B6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <f aca="false">[1]NOMBRES!G1</f>
+        <v>6.96</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>45628</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7"/>
+      <c r="B8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>2648.57</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>1072018.8360554</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7"/>
+      <c r="B12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7"/>
+      <c r="B13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>1006965023</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7"/>
+      <c r="B19" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="32"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7"/>
+      <c r="B20" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7"/>
+      <c r="B21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7"/>
+      <c r="B22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="38" t="n">
+        <v>5956713</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7"/>
+      <c r="B26" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7"/>
+      <c r="B27" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="14"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7"/>
+      <c r="B28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="14"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7"/>
+      <c r="B29" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="39" t="n">
+        <v>1500735</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7"/>
+      <c r="B30" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7"/>
+      <c r="B31" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="14"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7"/>
+      <c r="B32" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7"/>
+      <c r="B33" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="39" t="n">
+        <v>20633</v>
+      </c>
+      <c r="D33" s="14"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7"/>
+      <c r="B34" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="14"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7"/>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7"/>
+      <c r="B37" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7"/>
+      <c r="B38" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="46" t="n">
+        <v>1944.53</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7"/>
+      <c r="B39" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" s="47" t="n">
+        <v>0.9302</v>
+      </c>
+      <c r="D39" s="14"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7"/>
+      <c r="B40" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="50" t="n">
+        <v>1808.801806</v>
+      </c>
+      <c r="D40" s="14"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="49"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="B43:I45"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C19" type="list">
+      <formula1>#REF!</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="9" man="true" max="65535" min="0"/>
+  </colBreaks>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/hoja.xlsx
+++ b/docs/hoja.xlsx
@@ -852,9 +852,8 @@
           <cell r="P3">
             <v>1944.53</v>
           </cell>
-          <cell r="Q3">
-            <v>0.9302</v>
-          </cell>
+        </row>
+        <row r="3">
           <cell r="R3">
             <v>2648.57</v>
           </cell>
@@ -1170,7 +1169,7 @@
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">(F9/31.1035)*F6*C40</f>
-        <v>1072018.8360554</v>
+        <v>1129411.37318243</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>17</v>
@@ -1193,7 +1192,7 @@
       </c>
       <c r="F11" s="21" t="n">
         <f aca="false">F10*H11</f>
-        <v>19296.3390489972</v>
+        <v>20329.4047172837</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="22" t="n">
@@ -1217,7 +1216,7 @@
       </c>
       <c r="F12" s="21" t="n">
         <f aca="false">F10-F11</f>
-        <v>1052722.4970064</v>
+        <v>1109081.96846515</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
@@ -1615,8 +1614,7 @@
         <v>43</v>
       </c>
       <c r="C39" s="47" t="n">
-        <f aca="false">[1]NOMBRES!Q3</f>
-        <v>0.9302</v>
+        <v>0.98</v>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="13"/>
@@ -1633,7 +1631,7 @@
       </c>
       <c r="C40" s="48" t="n">
         <f aca="false">C39*C38</f>
-        <v>1808.801806</v>
+        <v>1905.6394</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="9"/>

--- a/docs/hoja.xlsx
+++ b/docs/hoja.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">CAJA DE SALUD APORTE 1,8%</t>
   </si>
   <si>
-    <t xml:space="preserve">si</t>
+    <t xml:space="preserve">no</t>
   </si>
   <si>
     <t xml:space="preserve">NOMBRE VENDEDOR</t>
@@ -690,9 +690,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2596320</xdr:colOff>
+      <xdr:colOff>2595960</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>188640</xdr:rowOff>
+      <xdr:rowOff>188280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -706,7 +706,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="459720" y="258480"/>
-          <a:ext cx="2337840" cy="621000"/>
+          <a:ext cx="2337480" cy="620640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -733,9 +733,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2596320</xdr:colOff>
+      <xdr:colOff>2595960</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>188640</xdr:rowOff>
+      <xdr:rowOff>188280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -749,7 +749,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="459720" y="258480"/>
-          <a:ext cx="2337840" cy="621000"/>
+          <a:ext cx="2337480" cy="620640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1061,7 +1061,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="F11" s="21" t="n">
         <f aca="false">F10*H11</f>
-        <v>20329.4047172837</v>
+        <v>0</v>
       </c>
       <c r="G11" s="13"/>
       <c r="H11" s="22" t="n">
         <f aca="false">IF(C20="NO",0,0.018)</f>
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="7"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="F12" s="21" t="n">
         <f aca="false">F10-F11</f>
-        <v>1109081.96846515</v>
+        <v>1129411.37318243</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
@@ -1767,7 +1767,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="21.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
